--- a/smoment/autopacmen_output/Mitocore_MitoMammal/Mitocore_MitoMammal_protein_data.xlsx
+++ b/smoment/autopacmen_output/Mitocore_MitoMammal/Mitocore_MitoMammal_protein_data.xlsx
@@ -1,16 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emanuel.lange\git\mitocore-smoment-model\smoment\autopacmen_output\Mitocore_MitoMammal\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F91C2E6-0D7D-49EC-8CB7-15613F066971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Total protein data" sheetId="1" r:id="rId1"/>
     <sheet name="Single protein data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -719,8 +725,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -779,17 +785,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -827,7 +841,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -861,6 +875,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -895,9 +910,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1070,27 +1086,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="79.1796875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1">
-        <v>0.8298543035192826</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>0.82985430351928258</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.06482551112599458</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>6.4825511125994578E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1104,11 +1123,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B229"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1116,1828 +1135,1828 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>1.67518680624112E-06</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>1.6751868062411201E-6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3">
-        <v>3.456615196427373E-06</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>3.4566151964273732E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4">
-        <v>1.221682168210311E-06</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>1.2216821682103111E-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5">
-        <v>1.504797147463184E-06</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>1.504797147463184E-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6">
-        <v>1.426556998024336E-06</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>1.426556998024336E-6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7">
-        <v>1.426556998024336E-06</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>1.426556998024336E-6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8">
-        <v>1.060393098650527E-06</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>1.060393098650527E-6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9">
-        <v>1.378122619800287E-06</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>1.3781226198002871E-6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10">
-        <v>1.751899033569715E-06</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>1.7518990335697151E-6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11">
-        <v>3.310116151181794E-06</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>3.3101161511817941E-6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12">
-        <v>3.626378874107301E-06</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>3.6263788741073008E-6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>16</v>
       </c>
       <c r="B13">
-        <v>1.099845101276661E-06</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>1.0998451012766609E-6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14">
-        <v>3.024525936940786E-06</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>3.024525936940786E-6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>18</v>
       </c>
       <c r="B15">
-        <v>1.842361565796831E-06</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>1.8423615657968309E-6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>19</v>
       </c>
       <c r="B16">
-        <v>2.358799566232647E-06</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>2.358799566232647E-6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>20</v>
       </c>
       <c r="B17">
-        <v>1.300809527799458E-06</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>1.3008095277994579E-6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18">
-        <v>1.065548273939687E-06</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>1.065548273939687E-6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>22</v>
       </c>
       <c r="B19">
-        <v>1.481240973438585E-06</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>1.481240973438585E-6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>23</v>
       </c>
       <c r="B20">
-        <v>1.246938736023957E-05</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>1.2469387360239569E-5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>24</v>
       </c>
       <c r="B21">
-        <v>3.028231781364436E-06</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>3.028231781364436E-6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>25</v>
       </c>
       <c r="B22">
-        <v>2.207377883333245E-06</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>2.207377883333245E-6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>26</v>
       </c>
       <c r="B23">
-        <v>1.585576062813027E-06</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>1.585576062813027E-6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>27</v>
       </c>
       <c r="B24">
-        <v>7.288520658155239E-06</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>7.2885206581552391E-6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25">
-        <v>8.074701869907916E-06</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>8.0747018699079158E-6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>29</v>
       </c>
       <c r="B26">
-        <v>6.123751212393504E-06</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>6.1237512123935037E-6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>30</v>
       </c>
       <c r="B27">
-        <v>2.197380353706621E-06</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>2.1973803537066208E-6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>31</v>
       </c>
       <c r="B28">
-        <v>8.544259052527585E-07</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>8.5442590525275853E-7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>32</v>
       </c>
       <c r="B29">
-        <v>1.7340589807026E-06</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>1.7340589807026E-6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>33</v>
       </c>
       <c r="B30">
-        <v>1.736432858705079E-06</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>1.7364328587050791E-6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>34</v>
       </c>
       <c r="B31">
-        <v>2.761717070306746E-06</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>2.7617170703067458E-6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>35</v>
       </c>
       <c r="B32">
-        <v>1.948989515462261E-07</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>1.948989515462261E-7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>36</v>
       </c>
       <c r="B33">
-        <v>1.639531827341914E-06</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>1.639531827341914E-6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>37</v>
       </c>
       <c r="B34">
-        <v>7.547686208773709E-06</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>7.5476862087737092E-6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>38</v>
       </c>
       <c r="B35">
-        <v>2.502410391489233E-06</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>2.5024103914892332E-6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>39</v>
       </c>
       <c r="B36">
-        <v>1.095050587068624E-06</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>1.095050587068624E-6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>40</v>
       </c>
       <c r="B37">
-        <v>2.065214962048422E-06</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>2.0652149620484219E-6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>41</v>
       </c>
       <c r="B38">
-        <v>2.961353907984251E-06</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>2.9613539079842509E-6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>42</v>
       </c>
       <c r="B39">
-        <v>4.483118851389506E-06</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>4.4831188513895058E-6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>43</v>
       </c>
       <c r="B40">
-        <v>4.340514281750485E-06</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>4.3405142817504854E-6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>44</v>
       </c>
       <c r="B41">
-        <v>1.039572322005957E-05</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>1.039572322005957E-5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>45</v>
       </c>
       <c r="B42">
-        <v>4.736539878238059E-06</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>4.7365398782380589E-6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>46</v>
       </c>
       <c r="B43">
-        <v>2.804653263839626E-05</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>2.8046532638396261E-5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>47</v>
       </c>
       <c r="B44">
-        <v>1.058764501118542E-05</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>1.0587645011185421E-5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>48</v>
       </c>
       <c r="B45">
-        <v>1.165525702993842E-06</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+        <v>1.1655257029938419E-6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46">
-        <v>7.676666829386899E-07</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+        <v>7.6766668293868988E-7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>50</v>
       </c>
       <c r="B47">
-        <v>1.948989515462261E-07</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>1.948989515462261E-7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>51</v>
       </c>
       <c r="B48">
-        <v>5.983532270986842E-07</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
+        <v>5.9835322709868422E-7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>52</v>
       </c>
       <c r="B49">
-        <v>1.805484780600718E-06</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>1.8054847806007181E-6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>53</v>
       </c>
       <c r="B50">
-        <v>7.218173214055606E-05</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
+        <v>7.2181732140556059E-5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>54</v>
       </c>
       <c r="B51">
-        <v>2.298770953122188E-05</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
+        <v>2.2987709531221881E-5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>55</v>
       </c>
       <c r="B52">
-        <v>8.236213797321209E-05</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
+        <v>8.2362137973212088E-5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>56</v>
       </c>
       <c r="B53">
-        <v>2.700882190608795E-06</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
+        <v>2.700882190608795E-6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>57</v>
       </c>
       <c r="B54">
-        <v>2.391928720750798E-05</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
+        <v>2.3919287207507979E-5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>58</v>
       </c>
       <c r="B55">
-        <v>8.788759519523985E-07</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
+        <v>8.7887595195239852E-7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>59</v>
       </c>
       <c r="B56">
-        <v>1.571860132696483E-06</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
+        <v>1.5718601326964829E-6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>60</v>
       </c>
       <c r="B57">
-        <v>3.409990977123058E-06</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
+        <v>3.409990977123058E-6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>61</v>
       </c>
       <c r="B58">
-        <v>2.176450949194911E-05</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
+        <v>2.1764509491949108E-5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>62</v>
       </c>
       <c r="B59">
-        <v>6.843630047064475E-05</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
+        <v>6.8436300470644751E-5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>63</v>
       </c>
       <c r="B60">
-        <v>1.146775008353406E-05</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
+        <v>1.1467750083534059E-5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>64</v>
       </c>
       <c r="B61">
-        <v>3.684716884308342E-05</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
+        <v>3.6847168843083423E-5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>65</v>
       </c>
       <c r="B62">
-        <v>2.659740231577057E-05</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
+        <v>2.6597402315770568E-5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>66</v>
       </c>
       <c r="B63">
-        <v>8.267158523264998E-07</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
+        <v>8.2671585232649983E-7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>67</v>
       </c>
       <c r="B64">
-        <v>2.531430637747051E-06</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
+        <v>2.531430637747051E-6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>68</v>
       </c>
       <c r="B65">
-        <v>2.11333164309867E-06</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
+        <v>2.1133316430986699E-6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>69</v>
       </c>
       <c r="B66">
-        <v>2.892255797512093E-06</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
+        <v>2.8922557975120931E-6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>70</v>
       </c>
       <c r="B67">
-        <v>3.797755127017695E-06</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
+        <v>3.7977551270176952E-6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>71</v>
       </c>
       <c r="B68">
-        <v>3.282609568088597E-05</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
+        <v>3.2826095680885971E-5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>72</v>
       </c>
       <c r="B69">
-        <v>5.156004121276101E-06</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
+        <v>5.1560041212761008E-6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>73</v>
       </c>
       <c r="B70">
-        <v>3.542730155833027E-06</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
+        <v>3.542730155833027E-6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>74</v>
       </c>
       <c r="B71">
-        <v>4.459840658269105E-06</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
+        <v>4.4598406582691049E-6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>75</v>
       </c>
       <c r="B72">
-        <v>3.278240534743743E-06</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
+        <v>3.2782405347437429E-6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>76</v>
       </c>
       <c r="B73">
-        <v>1.289787895991357E-06</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
+        <v>1.2897878959913569E-6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>77</v>
       </c>
       <c r="B74">
-        <v>8.504359043772754E-06</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
+        <v>8.5043590437727541E-6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>78</v>
       </c>
       <c r="B75">
-        <v>4.323040747584519E-06</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
+        <v>4.3230407475845193E-6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>79</v>
       </c>
       <c r="B76">
-        <v>1.236637963079414E-06</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
+        <v>1.2366379630794139E-6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>80</v>
       </c>
       <c r="B77">
-        <v>2.619239181037911E-06</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
+        <v>2.6192391810379111E-6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>81</v>
       </c>
       <c r="B78">
-        <v>1.22804660396928E-05</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
+        <v>1.22804660396928E-5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>82</v>
       </c>
       <c r="B79">
-        <v>3.475667906482841E-06</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
+        <v>3.4756679064828408E-6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>83</v>
       </c>
       <c r="B80">
-        <v>5.89210306733357E-06</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
+        <v>5.8921030673335701E-6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>84</v>
       </c>
       <c r="B81">
-        <v>9.319931176264791E-07</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
+        <v>9.3199311762647907E-7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>85</v>
       </c>
       <c r="B82">
-        <v>1.965056066496966E-05</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
+        <v>1.9650560664969661E-5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>86</v>
       </c>
       <c r="B83">
-        <v>5.57729723363913E-06</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
+        <v>5.5772972336391299E-6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>87</v>
       </c>
       <c r="B84">
-        <v>9.557368164254217E-06</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
+        <v>9.5573681642542169E-6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>88</v>
       </c>
       <c r="B85">
-        <v>3.13386915496184E-05</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
+        <v>3.1338691549618403E-5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>89</v>
       </c>
       <c r="B86">
-        <v>5.670692333247319E-06</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
+        <v>5.670692333247319E-6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>90</v>
       </c>
       <c r="B87">
-        <v>4.966141358637829E-06</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
+        <v>4.9661413586378286E-6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>91</v>
       </c>
       <c r="B88">
-        <v>4.453196784168978E-05</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
+        <v>4.4531967841689778E-5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>92</v>
       </c>
       <c r="B89">
-        <v>6.591013373774666E-06</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
+        <v>6.591013373774666E-6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>93</v>
       </c>
       <c r="B90">
-        <v>3.48829066566966E-06</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
+        <v>3.4882906656696601E-6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>94</v>
       </c>
       <c r="B91">
-        <v>6.130412350922549E-07</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
+        <v>6.1304123509225488E-7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>95</v>
       </c>
       <c r="B92">
-        <v>2.519021306855661E-06</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
+        <v>2.5190213068556612E-6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>96</v>
       </c>
       <c r="B93">
-        <v>1.008516587915798E-06</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
+        <v>1.0085165879157979E-6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>97</v>
       </c>
       <c r="B94">
-        <v>5.529838916446922E-06</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
+        <v>5.5298389164469218E-6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>98</v>
       </c>
       <c r="B95">
-        <v>3.351618302014076E-06</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
+        <v>3.3516183020140759E-6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>99</v>
       </c>
       <c r="B96">
-        <v>1.132280645106248E-05</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
+        <v>1.1322806451062481E-5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>100</v>
       </c>
       <c r="B97">
-        <v>7.792986935696541E-06</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
+        <v>7.7929869356965409E-6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>101</v>
       </c>
       <c r="B98">
-        <v>9.933630345788771E-06</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
+        <v>9.933630345788771E-6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>102</v>
       </c>
       <c r="B99">
-        <v>1.858187059386443E-06</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
+        <v>1.8581870593864429E-6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>103</v>
       </c>
       <c r="B100">
-        <v>2.434637856794207E-06</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
+        <v>2.4346378567942069E-6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>104</v>
       </c>
       <c r="B101">
-        <v>2.267484588449752E-06</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
+        <v>2.2674845884497519E-6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>105</v>
       </c>
       <c r="B102">
-        <v>4.477922826139416E-06</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
+        <v>4.4779228261394161E-6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>106</v>
       </c>
       <c r="B103">
-        <v>5.106951953930543E-07</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
+        <v>5.1069519539305428E-7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>107</v>
       </c>
       <c r="B104">
-        <v>4.500220233286074E-05</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2">
+        <v>4.5002202332860739E-5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>108</v>
       </c>
       <c r="B105">
-        <v>5.35508759203367E-06</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
+        <v>5.3550875920336701E-6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>109</v>
       </c>
       <c r="B106">
-        <v>8.58283193944065E-07</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
+        <v>8.5828319394406504E-7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>110</v>
       </c>
       <c r="B107">
-        <v>8.992272270474056E-06</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2">
+        <v>8.9922722704740562E-6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>111</v>
       </c>
       <c r="B108">
-        <v>3.485915005476489E-06</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2">
+        <v>3.4859150054764891E-6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>112</v>
       </c>
       <c r="B109">
-        <v>1.650179552803455E-06</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
+        <v>1.650179552803455E-6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>113</v>
       </c>
       <c r="B110">
-        <v>6.787637237698749E-06</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
+        <v>6.7876372376987491E-6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>114</v>
       </c>
       <c r="B111">
-        <v>2.276937638646571E-06</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
+        <v>2.2769376386465709E-6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>115</v>
       </c>
       <c r="B112">
-        <v>5.076095551142148E-06</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
+        <v>5.0760955511421483E-6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>116</v>
       </c>
       <c r="B113">
-        <v>1.143040192817378E-05</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
+        <v>1.143040192817378E-5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>117</v>
       </c>
       <c r="B114">
-        <v>1.980403540505955E-06</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
+        <v>1.9804035405059551E-6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>118</v>
       </c>
       <c r="B115">
-        <v>9.062795583255922E-06</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
+        <v>9.0627955832559222E-6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>119</v>
       </c>
       <c r="B116">
-        <v>1.331016105428673E-06</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
+        <v>1.3310161054286729E-6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>120</v>
       </c>
       <c r="B117">
-        <v>2.342013382036242E-06</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
+        <v>2.3420133820362418E-6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>121</v>
       </c>
       <c r="B118">
-        <v>6.47407225676651E-06</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
+        <v>6.4740722567665103E-6</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>122</v>
       </c>
       <c r="B119">
-        <v>1.522307376289641E-06</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
+        <v>1.5223073762896411E-6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>123</v>
       </c>
       <c r="B120">
-        <v>4.74125536794007E-06</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
+        <v>4.7412553679400696E-6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>124</v>
       </c>
       <c r="B121">
-        <v>2.217651842350467E-06</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2">
+        <v>2.217651842350467E-6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>125</v>
       </c>
       <c r="B122">
-        <v>2.504472436155411E-06</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2">
+        <v>2.5044724361554109E-6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>126</v>
       </c>
       <c r="B123">
-        <v>9.22449189209621E-06</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2">
+        <v>9.2244918920962096E-6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>127</v>
       </c>
       <c r="B124">
-        <v>8.300171244547212E-07</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2">
+        <v>8.3001712445472123E-7</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>128</v>
       </c>
       <c r="B125">
-        <v>5.343447675813301E-07</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
+        <v>5.3434476758133013E-7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>129</v>
       </c>
       <c r="B126">
-        <v>3.273067632301506E-06</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2">
+        <v>3.273067632301506E-6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>130</v>
       </c>
       <c r="B127">
-        <v>6.297786870078258E-07</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2">
+        <v>6.2977868700782581E-7</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>131</v>
       </c>
       <c r="B128">
-        <v>3.06865748383727E-06</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2">
+        <v>3.06865748383727E-6</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>132</v>
       </c>
       <c r="B129">
-        <v>1.082366365935968E-06</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2">
+        <v>1.0823663659359681E-6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>133</v>
       </c>
       <c r="B130">
-        <v>3.732033401489063E-06</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2">
+        <v>3.7320334014890628E-6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>134</v>
       </c>
       <c r="B131">
-        <v>2.330665391539916E-06</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
+        <v>2.3306653915399161E-6</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>135</v>
       </c>
       <c r="B132">
-        <v>2.039741425021821E-06</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
+        <v>2.0397414250218208E-6</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>136</v>
       </c>
       <c r="B133">
-        <v>1.007856370225037E-06</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
+        <v>1.007856370225037E-6</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>137</v>
       </c>
       <c r="B134">
-        <v>2.099724660587566E-06</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2">
+        <v>2.0997246605875661E-6</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>138</v>
       </c>
       <c r="B135">
-        <v>2.55669248991881E-06</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2">
+        <v>2.5566924899188099E-6</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>139</v>
       </c>
       <c r="B136">
-        <v>3.622497192274675E-06</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2">
+        <v>3.622497192274675E-6</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>140</v>
       </c>
       <c r="B137">
-        <v>4.805586270769223E-06</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2">
+        <v>4.8055862707692234E-6</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>141</v>
       </c>
       <c r="B138">
-        <v>7.021749977131203E-07</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2">
+        <v>7.0217499771312028E-7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>142</v>
       </c>
       <c r="B139">
-        <v>2.002102821379867E-06</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2">
+        <v>2.002102821379867E-6</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>143</v>
       </c>
       <c r="B140">
-        <v>8.184230676708476E-06</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2">
+        <v>8.1842306767084764E-6</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>144</v>
       </c>
       <c r="B141">
-        <v>7.23085167705362E-06</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2">
+        <v>7.2308516770536202E-6</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>145</v>
       </c>
       <c r="B142">
-        <v>1.405933189588144E-05</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2">
+        <v>1.405933189588144E-5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>146</v>
       </c>
       <c r="B143">
-        <v>6.182457457950898E-06</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
+        <v>6.1824574579508976E-6</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>147</v>
       </c>
       <c r="B144">
-        <v>1.557220018371833E-06</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
+        <v>1.5572200183718329E-6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>148</v>
       </c>
       <c r="B145">
-        <v>6.625024808814311E-06</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2">
+        <v>6.6250248088143107E-6</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>149</v>
       </c>
       <c r="B146">
-        <v>2.696103364466377E-06</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2">
+        <v>2.696103364466377E-6</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>150</v>
       </c>
       <c r="B147">
-        <v>1.315609001178544E-05</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
+        <v>1.3156090011785441E-5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>151</v>
       </c>
       <c r="B148">
-        <v>8.409413340426541E-07</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
+        <v>8.4094133404265412E-7</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>152</v>
       </c>
       <c r="B149">
-        <v>7.074927674673025E-07</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2">
+        <v>7.0749276746730249E-7</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>153</v>
       </c>
       <c r="B150">
-        <v>3.693980738091097E-06</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2">
+        <v>3.693980738091097E-6</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>154</v>
       </c>
       <c r="B151">
-        <v>5.507720994669062E-07</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2">
+        <v>5.5077209946690615E-7</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>155</v>
       </c>
       <c r="B152">
-        <v>1.590929333264724E-05</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2">
+        <v>1.5909293332647241E-5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>156</v>
       </c>
       <c r="B153">
-        <v>1.293411480558226E-06</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2">
+        <v>1.293411480558226E-6</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>157</v>
       </c>
       <c r="B154">
-        <v>1.996712170623188E-06</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
+        <v>1.9967121706231882E-6</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>158</v>
       </c>
       <c r="B155">
-        <v>3.207094241944579E-06</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
+        <v>3.2070942419445789E-6</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>159</v>
       </c>
       <c r="B156">
-        <v>5.855600670431235E-07</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
+        <v>5.8556006704312355E-7</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>160</v>
       </c>
       <c r="B157">
-        <v>1.313543448834889E-06</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
+        <v>1.3135434488348891E-6</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>161</v>
       </c>
       <c r="B158">
-        <v>1.227809032208411E-06</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
+        <v>1.227809032208411E-6</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>162</v>
       </c>
       <c r="B159">
-        <v>3.314439073828384E-06</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
+        <v>3.314439073828384E-6</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>163</v>
       </c>
       <c r="B160">
-        <v>8.074701971186209E-07</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
+        <v>8.0747019711862092E-7</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>164</v>
       </c>
       <c r="B161">
-        <v>1.085790952758445E-06</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
+        <v>1.085790952758445E-6</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>165</v>
       </c>
       <c r="B162">
-        <v>7.617577076377517E-07</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2">
+        <v>7.6175770763775171E-7</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>166</v>
       </c>
       <c r="B163">
-        <v>7.998070906503352E-07</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2">
+        <v>7.9980709065033521E-7</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>167</v>
       </c>
       <c r="B164">
-        <v>1.071747018010955E-06</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2">
+        <v>1.071747018010955E-6</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>168</v>
       </c>
       <c r="B165">
-        <v>5.952012598175687E-06</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2">
+        <v>5.9520125981756866E-6</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>169</v>
       </c>
       <c r="B166">
-        <v>6.310574975157483E-06</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2">
+        <v>6.3105749751574826E-6</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>170</v>
       </c>
       <c r="B167">
-        <v>2.973498087733267E-06</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2">
+        <v>2.973498087733267E-6</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>171</v>
       </c>
       <c r="B168">
-        <v>6.669215512875404E-06</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2">
+        <v>6.6692155128754043E-6</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>172</v>
       </c>
       <c r="B169">
-        <v>3.153116596334796E-06</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2">
+        <v>3.1531165963347961E-6</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>173</v>
       </c>
       <c r="B170">
-        <v>6.923554945000596E-06</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2">
+        <v>6.9235549450005959E-6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>174</v>
       </c>
       <c r="B171">
-        <v>1.149780419066029E-06</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2">
+        <v>1.149780419066029E-6</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>175</v>
       </c>
       <c r="B172">
-        <v>5.977140541969048E-06</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2">
+        <v>5.9771405419690484E-6</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>176</v>
       </c>
       <c r="B173">
-        <v>1.301055763841579E-06</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2">
+        <v>1.301055763841579E-6</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>177</v>
       </c>
       <c r="B174">
-        <v>4.571811005466034E-06</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2">
+        <v>4.5718110054660341E-6</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>178</v>
       </c>
       <c r="B175">
-        <v>8.892664875327192E-06</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2">
+        <v>8.8926648753271921E-6</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>179</v>
       </c>
       <c r="B176">
-        <v>5.621354029703237E-06</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2">
+        <v>5.6213540297032373E-6</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>180</v>
       </c>
       <c r="B177">
-        <v>1.086564517162992E-05</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2">
+        <v>1.086564517162992E-5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>181</v>
       </c>
       <c r="B178">
-        <v>2.875185219452707E-06</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2">
+        <v>2.8751852194527068E-6</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>182</v>
       </c>
       <c r="B179">
-        <v>3.441698209815833E-05</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2">
+        <v>3.4416982098158328E-5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>183</v>
       </c>
       <c r="B180">
-        <v>9.790233432341241E-07</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2">
+        <v>9.7902334323412408E-7</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>184</v>
       </c>
       <c r="B181">
-        <v>3.664225271975395E-06</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2">
+        <v>3.6642252719753952E-6</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>185</v>
       </c>
       <c r="B182">
-        <v>5.287124813705847E-06</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2">
+        <v>5.2871248137058468E-6</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>186</v>
       </c>
       <c r="B183">
-        <v>1.597237284923355E-06</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2">
+        <v>1.5972372849233549E-6</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>187</v>
       </c>
       <c r="B184">
-        <v>1.580551161312387E-06</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2">
+        <v>1.5805511613123869E-6</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>188</v>
       </c>
       <c r="B185">
-        <v>1.018324381564495E-06</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2">
+        <v>1.018324381564495E-6</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>189</v>
       </c>
       <c r="B186">
-        <v>8.451392835857569E-06</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2">
+        <v>8.4513928358575688E-6</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>190</v>
       </c>
       <c r="B187">
-        <v>5.156004121276101E-06</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2">
+        <v>5.1560041212761008E-6</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>191</v>
       </c>
       <c r="B188">
-        <v>6.522263118899893E-07</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2">
+        <v>6.5222631188998929E-7</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>192</v>
       </c>
       <c r="B189">
-        <v>5.339573090677745E-06</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2">
+        <v>5.339573090677745E-6</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>193</v>
       </c>
       <c r="B190">
-        <v>6.334619138895414E-07</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2">
+        <v>6.3346191388954136E-7</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>194</v>
       </c>
       <c r="B191">
-        <v>2.840203988750469E-06</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2">
+        <v>2.8402039887504691E-6</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>195</v>
       </c>
       <c r="B192">
-        <v>8.094700495328476E-07</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2">
+        <v>8.094700495328476E-7</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>196</v>
       </c>
       <c r="B193">
-        <v>1.718833418341872E-06</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2">
+        <v>1.7188334183418721E-6</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>197</v>
       </c>
       <c r="B194">
-        <v>2.813541465349372E-06</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2">
+        <v>2.8135414653493721E-6</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>198</v>
       </c>
       <c r="B195">
-        <v>3.531846536373114E-06</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2">
+        <v>3.5318465363731138E-6</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>199</v>
       </c>
       <c r="B196">
-        <v>1.744407605119657E-06</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2">
+        <v>1.7444076051196571E-6</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>200</v>
       </c>
       <c r="B197">
-        <v>4.279249325653509E-06</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2">
+        <v>4.2792493256535094E-6</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>201</v>
       </c>
       <c r="B198">
-        <v>4.940064417951542E-07</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2">
+        <v>4.9400644179515421E-7</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>202</v>
       </c>
       <c r="B199">
-        <v>1.737490648903075E-06</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2">
+        <v>1.737490648903075E-6</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>203</v>
       </c>
       <c r="B200">
-        <v>8.365292044033559E-07</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2">
+        <v>8.3652920440335594E-7</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>204</v>
       </c>
       <c r="B201">
-        <v>2.02528835436843E-06</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2">
+        <v>2.0252883543684299E-6</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>205</v>
       </c>
       <c r="B202">
-        <v>2.032193710347272E-06</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2">
+        <v>2.0321937103472721E-6</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>206</v>
       </c>
       <c r="B203">
-        <v>5.983532270986842E-07</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2">
+        <v>5.9835322709868422E-7</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>207</v>
       </c>
       <c r="B204">
-        <v>9.296070077529301E-07</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2">
+        <v>9.2960700775293009E-7</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>208</v>
       </c>
       <c r="B205">
-        <v>1.604077157312929E-06</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2">
+        <v>1.604077157312929E-6</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>209</v>
       </c>
       <c r="B206">
-        <v>4.618833322912076E-07</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2">
+        <v>4.6188333229120762E-7</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>210</v>
       </c>
       <c r="B207">
-        <v>3.454697041988805E-06</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2">
+        <v>3.454697041988805E-6</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>211</v>
       </c>
       <c r="B208">
-        <v>8.928819046297233E-07</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2">
+        <v>8.9288190462972332E-7</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>212</v>
       </c>
       <c r="B209">
-        <v>7.33064764361818E-07</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2">
+        <v>7.3306476436181796E-7</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>213</v>
       </c>
       <c r="B210">
-        <v>6.451267606633707E-07</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2">
+        <v>6.4512676066337075E-7</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>214</v>
       </c>
       <c r="B211">
-        <v>3.476448913322159E-06</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2">
+        <v>3.476448913322159E-6</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>215</v>
       </c>
       <c r="B212">
-        <v>5.621396901490184E-07</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2">
+        <v>5.6213969014901836E-7</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>216</v>
       </c>
       <c r="B213">
-        <v>3.422227396585297E-06</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2">
+        <v>3.4222273965852971E-6</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>217</v>
       </c>
       <c r="B214">
-        <v>1.353690357960803E-06</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2">
+        <v>1.3536903579608029E-6</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>218</v>
       </c>
       <c r="B215">
-        <v>9.782108064467993E-07</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2">
+        <v>9.7821080644679933E-7</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>219</v>
       </c>
       <c r="B216">
-        <v>9.041914400444472E-07</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2">
+        <v>9.0419144004444724E-7</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>220</v>
       </c>
       <c r="B217">
-        <v>1.649467612463319E-06</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2">
+        <v>1.6494676124633191E-6</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>221</v>
       </c>
       <c r="B218">
-        <v>2.565771140684722E-06</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2">
+        <v>2.5657711406847219E-6</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>222</v>
       </c>
       <c r="B219">
-        <v>1.859775603250551E-06</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2">
+        <v>1.8597756032505509E-6</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>223</v>
       </c>
       <c r="B220">
-        <v>1.639647340232517E-06</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2">
+        <v>1.639647340232517E-6</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>224</v>
       </c>
       <c r="B221">
-        <v>9.386692368894046E-07</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2">
+        <v>9.3866923688940461E-7</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>225</v>
       </c>
       <c r="B222">
-        <v>1.587893582039616E-06</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2">
+        <v>1.587893582039616E-6</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>226</v>
       </c>
       <c r="B223">
-        <v>5.762394001948995E-06</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2">
+        <v>5.7623940019489952E-6</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>227</v>
       </c>
       <c r="B224">
-        <v>1.225141739246699E-06</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2">
+        <v>1.225141739246699E-6</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>228</v>
       </c>
       <c r="B225">
-        <v>1.660361017064877E-06</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2">
+        <v>1.660361017064877E-6</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>229</v>
       </c>
       <c r="B226">
-        <v>7.643187238020601E-07</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2">
+        <v>7.6431872380206013E-7</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>230</v>
       </c>
       <c r="B227">
-        <v>2.089492147393363E-06</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2">
+        <v>2.089492147393363E-6</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>231</v>
       </c>
       <c r="B228">
-        <v>2.427909608284323E-06</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2">
+        <v>2.4279096082843229E-6</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>232</v>
       </c>
       <c r="B229">
-        <v>1.576189462593604E-06</v>
+        <v>1.576189462593604E-6</v>
       </c>
     </row>
   </sheetData>

--- a/smoment/autopacmen_output/Mitocore_MitoMammal/Mitocore_MitoMammal_protein_data.xlsx
+++ b/smoment/autopacmen_output/Mitocore_MitoMammal/Mitocore_MitoMammal_protein_data.xlsx
@@ -1,22 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emanuel.lange\git\mitocore-smoment-model\smoment\autopacmen_output\Mitocore_MitoMammal\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F91C2E6-0D7D-49EC-8CB7-15613F066971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Total protein data" sheetId="1" r:id="rId1"/>
     <sheet name="Single protein data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -725,8 +719,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -785,25 +779,17 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -841,7 +827,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -875,7 +861,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -910,10 +895,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1086,30 +1070,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="79.1796875" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1">
-        <v>0.82985430351928258</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>0.8298543035192826</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6.4825511125994578E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>0.06482551112599458</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1123,11 +1104,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B229"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1135,1828 +1116,1828 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>1.6751868062411201E-6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.67518680624112E-06</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3">
-        <v>3.4566151964273732E-6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.456615196427373E-06</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4">
-        <v>1.2216821682103111E-6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.221682168210311E-06</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5">
-        <v>1.504797147463184E-6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.504797147463184E-06</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6">
-        <v>1.426556998024336E-6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.426556998024336E-06</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7">
-        <v>1.426556998024336E-6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.426556998024336E-06</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8">
-        <v>1.060393098650527E-6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.060393098650527E-06</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9">
-        <v>1.3781226198002871E-6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.378122619800287E-06</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10">
-        <v>1.7518990335697151E-6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.751899033569715E-06</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11">
-        <v>3.3101161511817941E-6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.310116151181794E-06</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12">
-        <v>3.6263788741073008E-6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.626378874107301E-06</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
       <c r="B13">
-        <v>1.0998451012766609E-6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.099845101276661E-06</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14">
-        <v>3.024525936940786E-6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.024525936940786E-06</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>18</v>
       </c>
       <c r="B15">
-        <v>1.8423615657968309E-6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.842361565796831E-06</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>19</v>
       </c>
       <c r="B16">
-        <v>2.358799566232647E-6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.358799566232647E-06</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>20</v>
       </c>
       <c r="B17">
-        <v>1.3008095277994579E-6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.300809527799458E-06</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18">
-        <v>1.065548273939687E-6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.065548273939687E-06</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>22</v>
       </c>
       <c r="B19">
-        <v>1.481240973438585E-6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.481240973438585E-06</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>23</v>
       </c>
       <c r="B20">
-        <v>1.2469387360239569E-5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.246938736023957E-05</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>24</v>
       </c>
       <c r="B21">
-        <v>3.028231781364436E-6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.028231781364436E-06</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>25</v>
       </c>
       <c r="B22">
-        <v>2.207377883333245E-6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.207377883333245E-06</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>26</v>
       </c>
       <c r="B23">
-        <v>1.585576062813027E-6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.585576062813027E-06</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>27</v>
       </c>
       <c r="B24">
-        <v>7.2885206581552391E-6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+        <v>7.288520658155239E-06</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25">
-        <v>8.0747018699079158E-6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8.074701869907916E-06</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>29</v>
       </c>
       <c r="B26">
-        <v>6.1237512123935037E-6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+        <v>6.123751212393504E-06</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>30</v>
       </c>
       <c r="B27">
-        <v>2.1973803537066208E-6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.197380353706621E-06</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>31</v>
       </c>
       <c r="B28">
-        <v>8.5442590525275853E-7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8.544259052527585E-07</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>32</v>
       </c>
       <c r="B29">
-        <v>1.7340589807026E-6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.7340589807026E-06</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>33</v>
       </c>
       <c r="B30">
-        <v>1.7364328587050791E-6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.736432858705079E-06</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31" t="s">
         <v>34</v>
       </c>
       <c r="B31">
-        <v>2.7617170703067458E-6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.761717070306746E-06</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
         <v>35</v>
       </c>
       <c r="B32">
-        <v>1.948989515462261E-7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.948989515462261E-07</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
         <v>36</v>
       </c>
       <c r="B33">
-        <v>1.639531827341914E-6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.639531827341914E-06</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
         <v>37</v>
       </c>
       <c r="B34">
-        <v>7.5476862087737092E-6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+        <v>7.547686208773709E-06</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
         <v>38</v>
       </c>
       <c r="B35">
-        <v>2.5024103914892332E-6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.502410391489233E-06</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36" t="s">
         <v>39</v>
       </c>
       <c r="B36">
-        <v>1.095050587068624E-6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.095050587068624E-06</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37" t="s">
         <v>40</v>
       </c>
       <c r="B37">
-        <v>2.0652149620484219E-6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.065214962048422E-06</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38" t="s">
         <v>41</v>
       </c>
       <c r="B38">
-        <v>2.9613539079842509E-6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.961353907984251E-06</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39" t="s">
         <v>42</v>
       </c>
       <c r="B39">
-        <v>4.4831188513895058E-6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+        <v>4.483118851389506E-06</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
         <v>43</v>
       </c>
       <c r="B40">
-        <v>4.3405142817504854E-6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+        <v>4.340514281750485E-06</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41" t="s">
         <v>44</v>
       </c>
       <c r="B41">
-        <v>1.039572322005957E-5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.039572322005957E-05</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42" t="s">
         <v>45</v>
       </c>
       <c r="B42">
-        <v>4.7365398782380589E-6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+        <v>4.736539878238059E-06</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43" t="s">
         <v>46</v>
       </c>
       <c r="B43">
-        <v>2.8046532638396261E-5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.804653263839626E-05</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44" t="s">
         <v>47</v>
       </c>
       <c r="B44">
-        <v>1.0587645011185421E-5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.058764501118542E-05</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45" t="s">
         <v>48</v>
       </c>
       <c r="B45">
-        <v>1.1655257029938419E-6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.165525702993842E-06</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46">
-        <v>7.6766668293868988E-7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+        <v>7.676666829386899E-07</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47" t="s">
         <v>50</v>
       </c>
       <c r="B47">
-        <v>1.948989515462261E-7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.948989515462261E-07</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48" t="s">
         <v>51</v>
       </c>
       <c r="B48">
-        <v>5.9835322709868422E-7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5.983532270986842E-07</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>52</v>
       </c>
       <c r="B49">
-        <v>1.8054847806007181E-6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.805484780600718E-06</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50" t="s">
         <v>53</v>
       </c>
       <c r="B50">
-        <v>7.2181732140556059E-5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+        <v>7.218173214055606E-05</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
       <c r="A51" t="s">
         <v>54</v>
       </c>
       <c r="B51">
-        <v>2.2987709531221881E-5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.298770953122188E-05</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>55</v>
       </c>
       <c r="B52">
-        <v>8.2362137973212088E-5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8.236213797321209E-05</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
       <c r="A53" t="s">
         <v>56</v>
       </c>
       <c r="B53">
-        <v>2.700882190608795E-6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.700882190608795E-06</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
       <c r="A54" t="s">
         <v>57</v>
       </c>
       <c r="B54">
-        <v>2.3919287207507979E-5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.391928720750798E-05</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
       <c r="A55" t="s">
         <v>58</v>
       </c>
       <c r="B55">
-        <v>8.7887595195239852E-7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8.788759519523985E-07</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
       <c r="A56" t="s">
         <v>59</v>
       </c>
       <c r="B56">
-        <v>1.5718601326964829E-6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.571860132696483E-06</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>60</v>
       </c>
       <c r="B57">
-        <v>3.409990977123058E-6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.409990977123058E-06</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
       <c r="A58" t="s">
         <v>61</v>
       </c>
       <c r="B58">
-        <v>2.1764509491949108E-5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.176450949194911E-05</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>62</v>
       </c>
       <c r="B59">
-        <v>6.8436300470644751E-5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+        <v>6.843630047064475E-05</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
       <c r="A60" t="s">
         <v>63</v>
       </c>
       <c r="B60">
-        <v>1.1467750083534059E-5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.146775008353406E-05</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
       <c r="A61" t="s">
         <v>64</v>
       </c>
       <c r="B61">
-        <v>3.6847168843083423E-5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.684716884308342E-05</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
       <c r="A62" t="s">
         <v>65</v>
       </c>
       <c r="B62">
-        <v>2.6597402315770568E-5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.659740231577057E-05</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
       <c r="A63" t="s">
         <v>66</v>
       </c>
       <c r="B63">
-        <v>8.2671585232649983E-7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8.267158523264998E-07</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
       <c r="A64" t="s">
         <v>67</v>
       </c>
       <c r="B64">
-        <v>2.531430637747051E-6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.531430637747051E-06</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
       <c r="A65" t="s">
         <v>68</v>
       </c>
       <c r="B65">
-        <v>2.1133316430986699E-6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.11333164309867E-06</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
       <c r="A66" t="s">
         <v>69</v>
       </c>
       <c r="B66">
-        <v>2.8922557975120931E-6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.892255797512093E-06</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
       <c r="A67" t="s">
         <v>70</v>
       </c>
       <c r="B67">
-        <v>3.7977551270176952E-6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.797755127017695E-06</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
       <c r="A68" t="s">
         <v>71</v>
       </c>
       <c r="B68">
-        <v>3.2826095680885971E-5</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.282609568088597E-05</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
       <c r="A69" t="s">
         <v>72</v>
       </c>
       <c r="B69">
-        <v>5.1560041212761008E-6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5.156004121276101E-06</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
       <c r="A70" t="s">
         <v>73</v>
       </c>
       <c r="B70">
-        <v>3.542730155833027E-6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.542730155833027E-06</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
       <c r="A71" t="s">
         <v>74</v>
       </c>
       <c r="B71">
-        <v>4.4598406582691049E-6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+        <v>4.459840658269105E-06</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
       <c r="A72" t="s">
         <v>75</v>
       </c>
       <c r="B72">
-        <v>3.2782405347437429E-6</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.278240534743743E-06</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
       <c r="A73" t="s">
         <v>76</v>
       </c>
       <c r="B73">
-        <v>1.2897878959913569E-6</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.289787895991357E-06</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
       <c r="A74" t="s">
         <v>77</v>
       </c>
       <c r="B74">
-        <v>8.5043590437727541E-6</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8.504359043772754E-06</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
       <c r="A75" t="s">
         <v>78</v>
       </c>
       <c r="B75">
-        <v>4.3230407475845193E-6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+        <v>4.323040747584519E-06</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
       <c r="A76" t="s">
         <v>79</v>
       </c>
       <c r="B76">
-        <v>1.2366379630794139E-6</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.236637963079414E-06</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
       <c r="A77" t="s">
         <v>80</v>
       </c>
       <c r="B77">
-        <v>2.6192391810379111E-6</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.619239181037911E-06</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
       <c r="A78" t="s">
         <v>81</v>
       </c>
       <c r="B78">
-        <v>1.22804660396928E-5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.22804660396928E-05</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
       <c r="A79" t="s">
         <v>82</v>
       </c>
       <c r="B79">
-        <v>3.4756679064828408E-6</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.475667906482841E-06</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
       <c r="A80" t="s">
         <v>83</v>
       </c>
       <c r="B80">
-        <v>5.8921030673335701E-6</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5.89210306733357E-06</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
       <c r="A81" t="s">
         <v>84</v>
       </c>
       <c r="B81">
-        <v>9.3199311762647907E-7</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+        <v>9.319931176264791E-07</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
       <c r="A82" t="s">
         <v>85</v>
       </c>
       <c r="B82">
-        <v>1.9650560664969661E-5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.965056066496966E-05</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
       <c r="A83" t="s">
         <v>86</v>
       </c>
       <c r="B83">
-        <v>5.5772972336391299E-6</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5.57729723363913E-06</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
       <c r="A84" t="s">
         <v>87</v>
       </c>
       <c r="B84">
-        <v>9.5573681642542169E-6</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+        <v>9.557368164254217E-06</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
       <c r="A85" t="s">
         <v>88</v>
       </c>
       <c r="B85">
-        <v>3.1338691549618403E-5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.13386915496184E-05</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
       <c r="A86" t="s">
         <v>89</v>
       </c>
       <c r="B86">
-        <v>5.670692333247319E-6</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5.670692333247319E-06</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
       <c r="A87" t="s">
         <v>90</v>
       </c>
       <c r="B87">
-        <v>4.9661413586378286E-6</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+        <v>4.966141358637829E-06</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
       <c r="A88" t="s">
         <v>91</v>
       </c>
       <c r="B88">
-        <v>4.4531967841689778E-5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+        <v>4.453196784168978E-05</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
       <c r="A89" t="s">
         <v>92</v>
       </c>
       <c r="B89">
-        <v>6.591013373774666E-6</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+        <v>6.591013373774666E-06</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
       <c r="A90" t="s">
         <v>93</v>
       </c>
       <c r="B90">
-        <v>3.4882906656696601E-6</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.48829066566966E-06</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
       <c r="A91" t="s">
         <v>94</v>
       </c>
       <c r="B91">
-        <v>6.1304123509225488E-7</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+        <v>6.130412350922549E-07</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
       <c r="A92" t="s">
         <v>95</v>
       </c>
       <c r="B92">
-        <v>2.5190213068556612E-6</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.519021306855661E-06</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
       <c r="A93" t="s">
         <v>96</v>
       </c>
       <c r="B93">
-        <v>1.0085165879157979E-6</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.008516587915798E-06</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
       <c r="A94" t="s">
         <v>97</v>
       </c>
       <c r="B94">
-        <v>5.5298389164469218E-6</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5.529838916446922E-06</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
       <c r="A95" t="s">
         <v>98</v>
       </c>
       <c r="B95">
-        <v>3.3516183020140759E-6</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.351618302014076E-06</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
       <c r="A96" t="s">
         <v>99</v>
       </c>
       <c r="B96">
-        <v>1.1322806451062481E-5</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.132280645106248E-05</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
       <c r="A97" t="s">
         <v>100</v>
       </c>
       <c r="B97">
-        <v>7.7929869356965409E-6</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+        <v>7.792986935696541E-06</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
       <c r="A98" t="s">
         <v>101</v>
       </c>
       <c r="B98">
-        <v>9.933630345788771E-6</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+        <v>9.933630345788771E-06</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
       <c r="A99" t="s">
         <v>102</v>
       </c>
       <c r="B99">
-        <v>1.8581870593864429E-6</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.858187059386443E-06</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
       <c r="A100" t="s">
         <v>103</v>
       </c>
       <c r="B100">
-        <v>2.4346378567942069E-6</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.434637856794207E-06</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
       <c r="A101" t="s">
         <v>104</v>
       </c>
       <c r="B101">
-        <v>2.2674845884497519E-6</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.267484588449752E-06</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
       <c r="A102" t="s">
         <v>105</v>
       </c>
       <c r="B102">
-        <v>4.4779228261394161E-6</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+        <v>4.477922826139416E-06</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
       <c r="A103" t="s">
         <v>106</v>
       </c>
       <c r="B103">
-        <v>5.1069519539305428E-7</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5.106951953930543E-07</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
       <c r="A104" t="s">
         <v>107</v>
       </c>
       <c r="B104">
-        <v>4.5002202332860739E-5</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+        <v>4.500220233286074E-05</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
       <c r="A105" t="s">
         <v>108</v>
       </c>
       <c r="B105">
-        <v>5.3550875920336701E-6</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5.35508759203367E-06</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
       <c r="A106" t="s">
         <v>109</v>
       </c>
       <c r="B106">
-        <v>8.5828319394406504E-7</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8.58283193944065E-07</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
       <c r="A107" t="s">
         <v>110</v>
       </c>
       <c r="B107">
-        <v>8.9922722704740562E-6</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8.992272270474056E-06</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
       <c r="A108" t="s">
         <v>111</v>
       </c>
       <c r="B108">
-        <v>3.4859150054764891E-6</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.485915005476489E-06</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
       <c r="A109" t="s">
         <v>112</v>
       </c>
       <c r="B109">
-        <v>1.650179552803455E-6</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.650179552803455E-06</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
       <c r="A110" t="s">
         <v>113</v>
       </c>
       <c r="B110">
-        <v>6.7876372376987491E-6</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+        <v>6.787637237698749E-06</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
       <c r="A111" t="s">
         <v>114</v>
       </c>
       <c r="B111">
-        <v>2.2769376386465709E-6</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.276937638646571E-06</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
       <c r="A112" t="s">
         <v>115</v>
       </c>
       <c r="B112">
-        <v>5.0760955511421483E-6</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5.076095551142148E-06</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
       <c r="A113" t="s">
         <v>116</v>
       </c>
       <c r="B113">
-        <v>1.143040192817378E-5</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.143040192817378E-05</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
       <c r="A114" t="s">
         <v>117</v>
       </c>
       <c r="B114">
-        <v>1.9804035405059551E-6</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.980403540505955E-06</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
       <c r="A115" t="s">
         <v>118</v>
       </c>
       <c r="B115">
-        <v>9.0627955832559222E-6</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+        <v>9.062795583255922E-06</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
       <c r="A116" t="s">
         <v>119</v>
       </c>
       <c r="B116">
-        <v>1.3310161054286729E-6</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.331016105428673E-06</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
       <c r="A117" t="s">
         <v>120</v>
       </c>
       <c r="B117">
-        <v>2.3420133820362418E-6</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.342013382036242E-06</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
       <c r="A118" t="s">
         <v>121</v>
       </c>
       <c r="B118">
-        <v>6.4740722567665103E-6</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+        <v>6.47407225676651E-06</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
       <c r="A119" t="s">
         <v>122</v>
       </c>
       <c r="B119">
-        <v>1.5223073762896411E-6</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.522307376289641E-06</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
       <c r="A120" t="s">
         <v>123</v>
       </c>
       <c r="B120">
-        <v>4.7412553679400696E-6</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+        <v>4.74125536794007E-06</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
       <c r="A121" t="s">
         <v>124</v>
       </c>
       <c r="B121">
-        <v>2.217651842350467E-6</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.217651842350467E-06</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
       <c r="A122" t="s">
         <v>125</v>
       </c>
       <c r="B122">
-        <v>2.5044724361554109E-6</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.504472436155411E-06</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
       <c r="A123" t="s">
         <v>126</v>
       </c>
       <c r="B123">
-        <v>9.2244918920962096E-6</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+        <v>9.22449189209621E-06</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
       <c r="A124" t="s">
         <v>127</v>
       </c>
       <c r="B124">
-        <v>8.3001712445472123E-7</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8.300171244547212E-07</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
       <c r="A125" t="s">
         <v>128</v>
       </c>
       <c r="B125">
-        <v>5.3434476758133013E-7</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5.343447675813301E-07</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
       <c r="A126" t="s">
         <v>129</v>
       </c>
       <c r="B126">
-        <v>3.273067632301506E-6</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.273067632301506E-06</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
       <c r="A127" t="s">
         <v>130</v>
       </c>
       <c r="B127">
-        <v>6.2977868700782581E-7</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+        <v>6.297786870078258E-07</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
       <c r="A128" t="s">
         <v>131</v>
       </c>
       <c r="B128">
-        <v>3.06865748383727E-6</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.06865748383727E-06</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
       <c r="A129" t="s">
         <v>132</v>
       </c>
       <c r="B129">
-        <v>1.0823663659359681E-6</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.082366365935968E-06</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
       <c r="A130" t="s">
         <v>133</v>
       </c>
       <c r="B130">
-        <v>3.7320334014890628E-6</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.732033401489063E-06</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
       <c r="A131" t="s">
         <v>134</v>
       </c>
       <c r="B131">
-        <v>2.3306653915399161E-6</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.330665391539916E-06</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
       <c r="A132" t="s">
         <v>135</v>
       </c>
       <c r="B132">
-        <v>2.0397414250218208E-6</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.039741425021821E-06</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
       <c r="A133" t="s">
         <v>136</v>
       </c>
       <c r="B133">
-        <v>1.007856370225037E-6</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.007856370225037E-06</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
       <c r="A134" t="s">
         <v>137</v>
       </c>
       <c r="B134">
-        <v>2.0997246605875661E-6</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.099724660587566E-06</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
       <c r="A135" t="s">
         <v>138</v>
       </c>
       <c r="B135">
-        <v>2.5566924899188099E-6</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.55669248991881E-06</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
       <c r="A136" t="s">
         <v>139</v>
       </c>
       <c r="B136">
-        <v>3.622497192274675E-6</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.622497192274675E-06</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
       <c r="A137" t="s">
         <v>140</v>
       </c>
       <c r="B137">
-        <v>4.8055862707692234E-6</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+        <v>4.805586270769223E-06</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
       <c r="A138" t="s">
         <v>141</v>
       </c>
       <c r="B138">
-        <v>7.0217499771312028E-7</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+        <v>7.021749977131203E-07</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
       <c r="A139" t="s">
         <v>142</v>
       </c>
       <c r="B139">
-        <v>2.002102821379867E-6</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.002102821379867E-06</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
       <c r="A140" t="s">
         <v>143</v>
       </c>
       <c r="B140">
-        <v>8.1842306767084764E-6</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8.184230676708476E-06</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
       <c r="A141" t="s">
         <v>144</v>
       </c>
       <c r="B141">
-        <v>7.2308516770536202E-6</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+        <v>7.23085167705362E-06</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
       <c r="A142" t="s">
         <v>145</v>
       </c>
       <c r="B142">
-        <v>1.405933189588144E-5</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.405933189588144E-05</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
       <c r="A143" t="s">
         <v>146</v>
       </c>
       <c r="B143">
-        <v>6.1824574579508976E-6</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+        <v>6.182457457950898E-06</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
       <c r="A144" t="s">
         <v>147</v>
       </c>
       <c r="B144">
-        <v>1.5572200183718329E-6</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.557220018371833E-06</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
       <c r="A145" t="s">
         <v>148</v>
       </c>
       <c r="B145">
-        <v>6.6250248088143107E-6</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+        <v>6.625024808814311E-06</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
       <c r="A146" t="s">
         <v>149</v>
       </c>
       <c r="B146">
-        <v>2.696103364466377E-6</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.696103364466377E-06</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
       <c r="A147" t="s">
         <v>150</v>
       </c>
       <c r="B147">
-        <v>1.3156090011785441E-5</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.315609001178544E-05</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
       <c r="A148" t="s">
         <v>151</v>
       </c>
       <c r="B148">
-        <v>8.4094133404265412E-7</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8.409413340426541E-07</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
       <c r="A149" t="s">
         <v>152</v>
       </c>
       <c r="B149">
-        <v>7.0749276746730249E-7</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+        <v>7.074927674673025E-07</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
       <c r="A150" t="s">
         <v>153</v>
       </c>
       <c r="B150">
-        <v>3.693980738091097E-6</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.693980738091097E-06</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
       <c r="A151" t="s">
         <v>154</v>
       </c>
       <c r="B151">
-        <v>5.5077209946690615E-7</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5.507720994669062E-07</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
       <c r="A152" t="s">
         <v>155</v>
       </c>
       <c r="B152">
-        <v>1.5909293332647241E-5</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.590929333264724E-05</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
       <c r="A153" t="s">
         <v>156</v>
       </c>
       <c r="B153">
-        <v>1.293411480558226E-6</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.293411480558226E-06</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
       <c r="A154" t="s">
         <v>157</v>
       </c>
       <c r="B154">
-        <v>1.9967121706231882E-6</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.996712170623188E-06</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
       <c r="A155" t="s">
         <v>158</v>
       </c>
       <c r="B155">
-        <v>3.2070942419445789E-6</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.207094241944579E-06</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
       <c r="A156" t="s">
         <v>159</v>
       </c>
       <c r="B156">
-        <v>5.8556006704312355E-7</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5.855600670431235E-07</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
       <c r="A157" t="s">
         <v>160</v>
       </c>
       <c r="B157">
-        <v>1.3135434488348891E-6</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.313543448834889E-06</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
       <c r="A158" t="s">
         <v>161</v>
       </c>
       <c r="B158">
-        <v>1.227809032208411E-6</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.227809032208411E-06</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
       <c r="A159" t="s">
         <v>162</v>
       </c>
       <c r="B159">
-        <v>3.314439073828384E-6</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.314439073828384E-06</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
       <c r="A160" t="s">
         <v>163</v>
       </c>
       <c r="B160">
-        <v>8.0747019711862092E-7</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8.074701971186209E-07</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
       <c r="A161" t="s">
         <v>164</v>
       </c>
       <c r="B161">
-        <v>1.085790952758445E-6</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.085790952758445E-06</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
       <c r="A162" t="s">
         <v>165</v>
       </c>
       <c r="B162">
-        <v>7.6175770763775171E-7</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+        <v>7.617577076377517E-07</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
       <c r="A163" t="s">
         <v>166</v>
       </c>
       <c r="B163">
-        <v>7.9980709065033521E-7</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+        <v>7.998070906503352E-07</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
       <c r="A164" t="s">
         <v>167</v>
       </c>
       <c r="B164">
-        <v>1.071747018010955E-6</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.071747018010955E-06</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
       <c r="A165" t="s">
         <v>168</v>
       </c>
       <c r="B165">
-        <v>5.9520125981756866E-6</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5.952012598175687E-06</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
       <c r="A166" t="s">
         <v>169</v>
       </c>
       <c r="B166">
-        <v>6.3105749751574826E-6</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
+        <v>6.310574975157483E-06</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
       <c r="A167" t="s">
         <v>170</v>
       </c>
       <c r="B167">
-        <v>2.973498087733267E-6</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.973498087733267E-06</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
       <c r="A168" t="s">
         <v>171</v>
       </c>
       <c r="B168">
-        <v>6.6692155128754043E-6</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
+        <v>6.669215512875404E-06</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
       <c r="A169" t="s">
         <v>172</v>
       </c>
       <c r="B169">
-        <v>3.1531165963347961E-6</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.153116596334796E-06</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
       <c r="A170" t="s">
         <v>173</v>
       </c>
       <c r="B170">
-        <v>6.9235549450005959E-6</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
+        <v>6.923554945000596E-06</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
       <c r="A171" t="s">
         <v>174</v>
       </c>
       <c r="B171">
-        <v>1.149780419066029E-6</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.149780419066029E-06</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
       <c r="A172" t="s">
         <v>175</v>
       </c>
       <c r="B172">
-        <v>5.9771405419690484E-6</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5.977140541969048E-06</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
       <c r="A173" t="s">
         <v>176</v>
       </c>
       <c r="B173">
-        <v>1.301055763841579E-6</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.301055763841579E-06</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
       <c r="A174" t="s">
         <v>177</v>
       </c>
       <c r="B174">
-        <v>4.5718110054660341E-6</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
+        <v>4.571811005466034E-06</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
       <c r="A175" t="s">
         <v>178</v>
       </c>
       <c r="B175">
-        <v>8.8926648753271921E-6</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8.892664875327192E-06</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
       <c r="A176" t="s">
         <v>179</v>
       </c>
       <c r="B176">
-        <v>5.6213540297032373E-6</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5.621354029703237E-06</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
       <c r="A177" t="s">
         <v>180</v>
       </c>
       <c r="B177">
-        <v>1.086564517162992E-5</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.086564517162992E-05</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
       <c r="A178" t="s">
         <v>181</v>
       </c>
       <c r="B178">
-        <v>2.8751852194527068E-6</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.875185219452707E-06</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
       <c r="A179" t="s">
         <v>182</v>
       </c>
       <c r="B179">
-        <v>3.4416982098158328E-5</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.441698209815833E-05</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
       <c r="A180" t="s">
         <v>183</v>
       </c>
       <c r="B180">
-        <v>9.7902334323412408E-7</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
+        <v>9.790233432341241E-07</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
       <c r="A181" t="s">
         <v>184</v>
       </c>
       <c r="B181">
-        <v>3.6642252719753952E-6</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.664225271975395E-06</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
       <c r="A182" t="s">
         <v>185</v>
       </c>
       <c r="B182">
-        <v>5.2871248137058468E-6</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5.287124813705847E-06</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
       <c r="A183" t="s">
         <v>186</v>
       </c>
       <c r="B183">
-        <v>1.5972372849233549E-6</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.597237284923355E-06</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
       <c r="A184" t="s">
         <v>187</v>
       </c>
       <c r="B184">
-        <v>1.5805511613123869E-6</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.580551161312387E-06</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
       <c r="A185" t="s">
         <v>188</v>
       </c>
       <c r="B185">
-        <v>1.018324381564495E-6</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.018324381564495E-06</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
       <c r="A186" t="s">
         <v>189</v>
       </c>
       <c r="B186">
-        <v>8.4513928358575688E-6</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8.451392835857569E-06</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
       <c r="A187" t="s">
         <v>190</v>
       </c>
       <c r="B187">
-        <v>5.1560041212761008E-6</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5.156004121276101E-06</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
       <c r="A188" t="s">
         <v>191</v>
       </c>
       <c r="B188">
-        <v>6.5222631188998929E-7</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
+        <v>6.522263118899893E-07</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
       <c r="A189" t="s">
         <v>192</v>
       </c>
       <c r="B189">
-        <v>5.339573090677745E-6</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5.339573090677745E-06</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
       <c r="A190" t="s">
         <v>193</v>
       </c>
       <c r="B190">
-        <v>6.3346191388954136E-7</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
+        <v>6.334619138895414E-07</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
       <c r="A191" t="s">
         <v>194</v>
       </c>
       <c r="B191">
-        <v>2.8402039887504691E-6</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.840203988750469E-06</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
       <c r="A192" t="s">
         <v>195</v>
       </c>
       <c r="B192">
-        <v>8.094700495328476E-7</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8.094700495328476E-07</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
       <c r="A193" t="s">
         <v>196</v>
       </c>
       <c r="B193">
-        <v>1.7188334183418721E-6</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.718833418341872E-06</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
       <c r="A194" t="s">
         <v>197</v>
       </c>
       <c r="B194">
-        <v>2.8135414653493721E-6</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.813541465349372E-06</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
       <c r="A195" t="s">
         <v>198</v>
       </c>
       <c r="B195">
-        <v>3.5318465363731138E-6</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.531846536373114E-06</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
       <c r="A196" t="s">
         <v>199</v>
       </c>
       <c r="B196">
-        <v>1.7444076051196571E-6</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.744407605119657E-06</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
       <c r="A197" t="s">
         <v>200</v>
       </c>
       <c r="B197">
-        <v>4.2792493256535094E-6</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
+        <v>4.279249325653509E-06</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
       <c r="A198" t="s">
         <v>201</v>
       </c>
       <c r="B198">
-        <v>4.9400644179515421E-7</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
+        <v>4.940064417951542E-07</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
       <c r="A199" t="s">
         <v>202</v>
       </c>
       <c r="B199">
-        <v>1.737490648903075E-6</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.737490648903075E-06</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
       <c r="A200" t="s">
         <v>203</v>
       </c>
       <c r="B200">
-        <v>8.3652920440335594E-7</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8.365292044033559E-07</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
       <c r="A201" t="s">
         <v>204</v>
       </c>
       <c r="B201">
-        <v>2.0252883543684299E-6</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.02528835436843E-06</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
       <c r="A202" t="s">
         <v>205</v>
       </c>
       <c r="B202">
-        <v>2.0321937103472721E-6</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.032193710347272E-06</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
       <c r="A203" t="s">
         <v>206</v>
       </c>
       <c r="B203">
-        <v>5.9835322709868422E-7</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5.983532270986842E-07</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
       <c r="A204" t="s">
         <v>207</v>
       </c>
       <c r="B204">
-        <v>9.2960700775293009E-7</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
+        <v>9.296070077529301E-07</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
       <c r="A205" t="s">
         <v>208</v>
       </c>
       <c r="B205">
-        <v>1.604077157312929E-6</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.604077157312929E-06</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
       <c r="A206" t="s">
         <v>209</v>
       </c>
       <c r="B206">
-        <v>4.6188333229120762E-7</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
+        <v>4.618833322912076E-07</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
       <c r="A207" t="s">
         <v>210</v>
       </c>
       <c r="B207">
-        <v>3.454697041988805E-6</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.454697041988805E-06</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
       <c r="A208" t="s">
         <v>211</v>
       </c>
       <c r="B208">
-        <v>8.9288190462972332E-7</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8.928819046297233E-07</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
       <c r="A209" t="s">
         <v>212</v>
       </c>
       <c r="B209">
-        <v>7.3306476436181796E-7</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.35">
+        <v>7.33064764361818E-07</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
       <c r="A210" t="s">
         <v>213</v>
       </c>
       <c r="B210">
-        <v>6.4512676066337075E-7</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.35">
+        <v>6.451267606633707E-07</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
       <c r="A211" t="s">
         <v>214</v>
       </c>
       <c r="B211">
-        <v>3.476448913322159E-6</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.476448913322159E-06</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
       <c r="A212" t="s">
         <v>215</v>
       </c>
       <c r="B212">
-        <v>5.6213969014901836E-7</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5.621396901490184E-07</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
       <c r="A213" t="s">
         <v>216</v>
       </c>
       <c r="B213">
-        <v>3.4222273965852971E-6</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3.422227396585297E-06</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
       <c r="A214" t="s">
         <v>217</v>
       </c>
       <c r="B214">
-        <v>1.3536903579608029E-6</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.353690357960803E-06</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
       <c r="A215" t="s">
         <v>218</v>
       </c>
       <c r="B215">
-        <v>9.7821080644679933E-7</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.35">
+        <v>9.782108064467993E-07</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
       <c r="A216" t="s">
         <v>219</v>
       </c>
       <c r="B216">
-        <v>9.0419144004444724E-7</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.35">
+        <v>9.041914400444472E-07</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
       <c r="A217" t="s">
         <v>220</v>
       </c>
       <c r="B217">
-        <v>1.6494676124633191E-6</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.649467612463319E-06</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
       <c r="A218" t="s">
         <v>221</v>
       </c>
       <c r="B218">
-        <v>2.5657711406847219E-6</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.565771140684722E-06</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
       <c r="A219" t="s">
         <v>222</v>
       </c>
       <c r="B219">
-        <v>1.8597756032505509E-6</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.859775603250551E-06</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
       <c r="A220" t="s">
         <v>223</v>
       </c>
       <c r="B220">
-        <v>1.639647340232517E-6</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.639647340232517E-06</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
       <c r="A221" t="s">
         <v>224</v>
       </c>
       <c r="B221">
-        <v>9.3866923688940461E-7</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.35">
+        <v>9.386692368894046E-07</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
       <c r="A222" t="s">
         <v>225</v>
       </c>
       <c r="B222">
-        <v>1.587893582039616E-6</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.587893582039616E-06</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
       <c r="A223" t="s">
         <v>226</v>
       </c>
       <c r="B223">
-        <v>5.7623940019489952E-6</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5.762394001948995E-06</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
       <c r="A224" t="s">
         <v>227</v>
       </c>
       <c r="B224">
-        <v>1.225141739246699E-6</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.225141739246699E-06</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
       <c r="A225" t="s">
         <v>228</v>
       </c>
       <c r="B225">
-        <v>1.660361017064877E-6</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.660361017064877E-06</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
       <c r="A226" t="s">
         <v>229</v>
       </c>
       <c r="B226">
-        <v>7.6431872380206013E-7</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.35">
+        <v>7.643187238020601E-07</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
       <c r="A227" t="s">
         <v>230</v>
       </c>
       <c r="B227">
-        <v>2.089492147393363E-6</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.089492147393363E-06</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
       <c r="A228" t="s">
         <v>231</v>
       </c>
       <c r="B228">
-        <v>2.4279096082843229E-6</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.427909608284323E-06</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
       <c r="A229" t="s">
         <v>232</v>
       </c>
       <c r="B229">
-        <v>1.576189462593604E-6</v>
+        <v>1.576189462593604E-06</v>
       </c>
     </row>
   </sheetData>
